--- a/public/data/ministries_pvp.xlsx
+++ b/public/data/ministries_pvp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\vacantPositionsPowerBI\OPSC PVP Dashboard\psc-pvp-dashboard\public\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stasombo\OneDrive - Vanuatu Gov\Documents\GitHub\psc-pvp-dashboard\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{461D5CA6-4FBA-4753-8DD2-736FE7C3B445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2A8362C-32A5-4277-BA16-C2A80FCC1F11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ministries_pvp" sheetId="1" r:id="rId1"/>
@@ -19,16 +19,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ministries_pvp!$A$1:$G$267</definedName>
   </definedNames>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="370">
   <si>
     <t>MINISTRY</t>
   </si>
@@ -1143,7 +1138,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1690,9 +1685,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1730,7 +1725,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1836,7 +1831,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1978,30 +1973,30 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q267"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:Q273"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="50.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="50.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="3.88671875" customWidth="1"/>
-    <col min="16" max="16" width="5.109375" customWidth="1"/>
-    <col min="17" max="17" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.85546875" customWidth="1"/>
+    <col min="16" max="16" width="5.140625" customWidth="1"/>
+    <col min="17" max="17" width="26.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2027,7 +2022,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2053,7 +2048,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2079,7 +2074,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -2105,7 +2100,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -2131,7 +2126,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2157,7 +2152,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2183,7 +2178,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -2209,7 +2204,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -2235,7 +2230,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -2261,7 +2256,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -2287,7 +2282,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -2310,7 +2305,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -2333,7 +2328,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>8</v>
       </c>
@@ -2356,7 +2351,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>8</v>
       </c>
@@ -2379,7 +2374,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>8</v>
       </c>
@@ -2402,7 +2397,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>8</v>
       </c>
@@ -2425,7 +2420,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>8</v>
       </c>
@@ -2448,7 +2443,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -2471,7 +2466,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>8</v>
       </c>
@@ -2494,7 +2489,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -2517,7 +2512,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -2540,7 +2535,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -2563,7 +2558,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>8</v>
       </c>
@@ -2586,7 +2581,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>8</v>
       </c>
@@ -2609,7 +2604,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>8</v>
       </c>
@@ -2632,7 +2627,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>8</v>
       </c>
@@ -2655,7 +2650,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>8</v>
       </c>
@@ -2678,7 +2673,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>8</v>
       </c>
@@ -2698,7 +2693,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>8</v>
       </c>
@@ -2721,7 +2716,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>8</v>
       </c>
@@ -2744,7 +2739,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>8</v>
       </c>
@@ -2767,7 +2762,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>8</v>
       </c>
@@ -2790,7 +2785,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>8</v>
       </c>
@@ -2813,7 +2808,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>8</v>
       </c>
@@ -2836,7 +2831,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>8</v>
       </c>
@@ -2859,7 +2854,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>8</v>
       </c>
@@ -2882,7 +2877,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>8</v>
       </c>
@@ -2905,7 +2900,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>8</v>
       </c>
@@ -2928,7 +2923,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>8</v>
       </c>
@@ -2951,7 +2946,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>8</v>
       </c>
@@ -2974,7 +2969,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>8</v>
       </c>
@@ -2997,7 +2992,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>8</v>
       </c>
@@ -3020,7 +3015,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>8</v>
       </c>
@@ -3043,7 +3038,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>8</v>
       </c>
@@ -3066,7 +3061,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>8</v>
       </c>
@@ -3089,7 +3084,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>8</v>
       </c>
@@ -3112,7 +3107,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>8</v>
       </c>
@@ -3135,7 +3130,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>8</v>
       </c>
@@ -3158,7 +3153,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>8</v>
       </c>
@@ -3181,7 +3176,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>8</v>
       </c>
@@ -3204,7 +3199,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>8</v>
       </c>
@@ -3227,7 +3222,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>8</v>
       </c>
@@ -3250,7 +3245,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>8</v>
       </c>
@@ -3273,7 +3268,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>8</v>
       </c>
@@ -3296,7 +3291,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>8</v>
       </c>
@@ -3319,7 +3314,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>8</v>
       </c>
@@ -3342,7 +3337,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>8</v>
       </c>
@@ -3365,7 +3360,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>8</v>
       </c>
@@ -3388,7 +3383,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>8</v>
       </c>
@@ -3411,7 +3406,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>8</v>
       </c>
@@ -3434,7 +3429,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>8</v>
       </c>
@@ -3457,7 +3452,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>8</v>
       </c>
@@ -3480,7 +3475,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>8</v>
       </c>
@@ -3503,7 +3498,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>8</v>
       </c>
@@ -3526,7 +3521,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>8</v>
       </c>
@@ -3549,7 +3544,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>8</v>
       </c>
@@ -3572,7 +3567,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>8</v>
       </c>
@@ -3595,7 +3590,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>8</v>
       </c>
@@ -3618,7 +3613,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>8</v>
       </c>
@@ -3641,7 +3636,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>8</v>
       </c>
@@ -3664,7 +3659,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>8</v>
       </c>
@@ -3687,7 +3682,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>8</v>
       </c>
@@ -3710,7 +3705,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>8</v>
       </c>
@@ -3733,7 +3728,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>123</v>
       </c>
@@ -3753,7 +3748,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>123</v>
       </c>
@@ -3773,7 +3768,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>123</v>
       </c>
@@ -3793,7 +3788,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>123</v>
       </c>
@@ -3813,7 +3808,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>123</v>
       </c>
@@ -3833,7 +3828,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>133</v>
       </c>
@@ -3856,7 +3851,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="81" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>133</v>
       </c>
@@ -3879,7 +3874,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="82" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>133</v>
       </c>
@@ -3902,7 +3897,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="83" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>133</v>
       </c>
@@ -3925,7 +3920,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="84" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>133</v>
       </c>
@@ -3948,7 +3943,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="85" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>133</v>
       </c>
@@ -3971,7 +3966,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="86" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>133</v>
       </c>
@@ -3994,7 +3989,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="87" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>133</v>
       </c>
@@ -4017,7 +4012,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="88" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>133</v>
       </c>
@@ -4040,7 +4035,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="89" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>133</v>
       </c>
@@ -4063,7 +4058,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="90" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>133</v>
       </c>
@@ -4086,7 +4081,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="91" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>133</v>
       </c>
@@ -4109,7 +4104,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="92" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>133</v>
       </c>
@@ -4132,7 +4127,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="93" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>133</v>
       </c>
@@ -4155,7 +4150,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="94" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>133</v>
       </c>
@@ -4178,7 +4173,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="95" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>133</v>
       </c>
@@ -4201,7 +4196,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="96" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>133</v>
       </c>
@@ -4224,7 +4219,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="97" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>133</v>
       </c>
@@ -4247,7 +4242,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="98" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>133</v>
       </c>
@@ -4270,7 +4265,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="99" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>158</v>
       </c>
@@ -4293,7 +4288,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="100" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>158</v>
       </c>
@@ -4316,7 +4311,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>158</v>
       </c>
@@ -4336,7 +4331,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>158</v>
       </c>
@@ -4356,7 +4351,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>158</v>
       </c>
@@ -4376,7 +4371,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>158</v>
       </c>
@@ -4396,7 +4391,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>158</v>
       </c>
@@ -4419,7 +4414,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>158</v>
       </c>
@@ -4442,7 +4437,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>158</v>
       </c>
@@ -4465,7 +4460,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>158</v>
       </c>
@@ -4488,7 +4483,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>158</v>
       </c>
@@ -4511,7 +4506,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>158</v>
       </c>
@@ -4534,7 +4529,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>158</v>
       </c>
@@ -4557,7 +4552,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>158</v>
       </c>
@@ -4580,7 +4575,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>158</v>
       </c>
@@ -4603,7 +4598,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>158</v>
       </c>
@@ -4626,7 +4621,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>158</v>
       </c>
@@ -4649,7 +4644,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>158</v>
       </c>
@@ -4669,7 +4664,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>158</v>
       </c>
@@ -4683,7 +4678,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>158</v>
       </c>
@@ -4703,7 +4698,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="119" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>158</v>
       </c>
@@ -4723,7 +4718,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="120" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>158</v>
       </c>
@@ -4746,7 +4741,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="121" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>158</v>
       </c>
@@ -4769,7 +4764,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="122" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>199</v>
       </c>
@@ -4792,7 +4787,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="123" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>199</v>
       </c>
@@ -4815,7 +4810,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="124" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>199</v>
       </c>
@@ -4838,7 +4833,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="125" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>199</v>
       </c>
@@ -4861,7 +4856,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>199</v>
       </c>
@@ -4884,7 +4879,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>199</v>
       </c>
@@ -4907,7 +4902,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>199</v>
       </c>
@@ -4930,7 +4925,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="129" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>199</v>
       </c>
@@ -4953,7 +4948,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>199</v>
       </c>
@@ -4976,7 +4971,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>199</v>
       </c>
@@ -4999,7 +4994,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>199</v>
       </c>
@@ -5022,7 +5017,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>199</v>
       </c>
@@ -5045,7 +5040,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>199</v>
       </c>
@@ -5068,7 +5063,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>199</v>
       </c>
@@ -5091,7 +5086,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>199</v>
       </c>
@@ -5114,7 +5109,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>199</v>
       </c>
@@ -5137,7 +5132,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>199</v>
       </c>
@@ -5160,7 +5155,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>199</v>
       </c>
@@ -5183,7 +5178,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>199</v>
       </c>
@@ -5206,7 +5201,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>199</v>
       </c>
@@ -5229,7 +5224,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>199</v>
       </c>
@@ -5252,7 +5247,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>199</v>
       </c>
@@ -5275,7 +5270,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>199</v>
       </c>
@@ -5298,7 +5293,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>199</v>
       </c>
@@ -5321,7 +5316,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>199</v>
       </c>
@@ -5344,7 +5339,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>199</v>
       </c>
@@ -5367,7 +5362,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>199</v>
       </c>
@@ -5390,7 +5385,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>199</v>
       </c>
@@ -5413,7 +5408,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>199</v>
       </c>
@@ -5436,7 +5431,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>199</v>
       </c>
@@ -5459,7 +5454,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>199</v>
       </c>
@@ -5482,7 +5477,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>199</v>
       </c>
@@ -5505,7 +5500,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>199</v>
       </c>
@@ -5528,7 +5523,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>199</v>
       </c>
@@ -5551,7 +5546,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>199</v>
       </c>
@@ -5574,7 +5569,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>199</v>
       </c>
@@ -5597,7 +5592,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>199</v>
       </c>
@@ -5620,7 +5615,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>199</v>
       </c>
@@ -5643,7 +5638,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>199</v>
       </c>
@@ -5666,7 +5661,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>199</v>
       </c>
@@ -5689,7 +5684,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>199</v>
       </c>
@@ -5712,7 +5707,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>199</v>
       </c>
@@ -5735,7 +5730,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>199</v>
       </c>
@@ -5758,7 +5753,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>199</v>
       </c>
@@ -5778,7 +5773,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>199</v>
       </c>
@@ -5801,7 +5796,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>199</v>
       </c>
@@ -5824,7 +5819,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>244</v>
       </c>
@@ -5847,7 +5842,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>244</v>
       </c>
@@ -5870,7 +5865,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>244</v>
       </c>
@@ -5893,7 +5888,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>244</v>
       </c>
@@ -5916,7 +5911,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>244</v>
       </c>
@@ -5939,7 +5934,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>244</v>
       </c>
@@ -5962,7 +5957,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>244</v>
       </c>
@@ -5985,7 +5980,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>244</v>
       </c>
@@ -6008,7 +6003,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>244</v>
       </c>
@@ -6031,7 +6026,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>244</v>
       </c>
@@ -6054,7 +6049,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>244</v>
       </c>
@@ -6077,7 +6072,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>244</v>
       </c>
@@ -6100,7 +6095,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>244</v>
       </c>
@@ -6123,7 +6118,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>244</v>
       </c>
@@ -6146,7 +6141,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>244</v>
       </c>
@@ -6169,7 +6164,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>267</v>
       </c>
@@ -6192,7 +6187,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>267</v>
       </c>
@@ -6215,7 +6210,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>267</v>
       </c>
@@ -6238,7 +6233,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>267</v>
       </c>
@@ -6261,7 +6256,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>267</v>
       </c>
@@ -6284,7 +6279,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>267</v>
       </c>
@@ -6307,7 +6302,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>267</v>
       </c>
@@ -6330,7 +6325,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>267</v>
       </c>
@@ -6353,7 +6348,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>267</v>
       </c>
@@ -6376,7 +6371,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>267</v>
       </c>
@@ -6399,7 +6394,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>267</v>
       </c>
@@ -6422,7 +6417,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>267</v>
       </c>
@@ -6445,7 +6440,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>267</v>
       </c>
@@ -6468,7 +6463,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>267</v>
       </c>
@@ -6491,7 +6486,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>267</v>
       </c>
@@ -6514,7 +6509,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>267</v>
       </c>
@@ -6537,7 +6532,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>267</v>
       </c>
@@ -6560,7 +6555,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>267</v>
       </c>
@@ -6583,7 +6578,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>267</v>
       </c>
@@ -6606,7 +6601,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>267</v>
       </c>
@@ -6629,7 +6624,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>290</v>
       </c>
@@ -6652,7 +6647,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>290</v>
       </c>
@@ -6675,7 +6670,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>293</v>
       </c>
@@ -6698,7 +6693,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>293</v>
       </c>
@@ -6718,7 +6713,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>293</v>
       </c>
@@ -6741,7 +6736,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>293</v>
       </c>
@@ -6764,7 +6759,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>293</v>
       </c>
@@ -6787,7 +6782,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>293</v>
       </c>
@@ -6810,7 +6805,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>293</v>
       </c>
@@ -6833,7 +6828,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>293</v>
       </c>
@@ -6856,7 +6851,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>293</v>
       </c>
@@ -6879,7 +6874,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>293</v>
       </c>
@@ -6902,7 +6897,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>293</v>
       </c>
@@ -6925,7 +6920,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>293</v>
       </c>
@@ -6948,7 +6943,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>310</v>
       </c>
@@ -6968,7 +6963,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>310</v>
       </c>
@@ -6988,7 +6983,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>315</v>
       </c>
@@ -7011,7 +7006,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>315</v>
       </c>
@@ -7034,7 +7029,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>315</v>
       </c>
@@ -7057,7 +7052,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>315</v>
       </c>
@@ -7080,7 +7075,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>315</v>
       </c>
@@ -7103,7 +7098,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>315</v>
       </c>
@@ -7126,7 +7121,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>315</v>
       </c>
@@ -7149,7 +7144,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>315</v>
       </c>
@@ -7172,7 +7167,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>315</v>
       </c>
@@ -7195,7 +7190,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>330</v>
       </c>
@@ -7218,7 +7213,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>330</v>
       </c>
@@ -7241,7 +7236,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>330</v>
       </c>
@@ -7264,7 +7259,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>330</v>
       </c>
@@ -7287,7 +7282,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>330</v>
       </c>
@@ -7310,7 +7305,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>330</v>
       </c>
@@ -7333,7 +7328,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>330</v>
       </c>
@@ -7356,7 +7351,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>330</v>
       </c>
@@ -7379,7 +7374,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>330</v>
       </c>
@@ -7402,7 +7397,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>330</v>
       </c>
@@ -7425,7 +7420,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>330</v>
       </c>
@@ -7448,7 +7443,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>337</v>
       </c>
@@ -7471,7 +7466,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>337</v>
       </c>
@@ -7494,7 +7489,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>337</v>
       </c>
@@ -7517,7 +7512,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>337</v>
       </c>
@@ -7540,7 +7535,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>337</v>
       </c>
@@ -7563,7 +7558,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>337</v>
       </c>
@@ -7586,7 +7581,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>337</v>
       </c>
@@ -7609,7 +7604,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>337</v>
       </c>
@@ -7632,7 +7627,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>337</v>
       </c>
@@ -7655,7 +7650,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>337</v>
       </c>
@@ -7678,7 +7673,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>337</v>
       </c>
@@ -7701,7 +7696,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>337</v>
       </c>
@@ -7724,7 +7719,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>337</v>
       </c>
@@ -7747,7 +7742,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>337</v>
       </c>
@@ -7770,7 +7765,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>337</v>
       </c>
@@ -7793,7 +7788,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>337</v>
       </c>
@@ -7816,7 +7811,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>337</v>
       </c>
@@ -7839,7 +7834,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>337</v>
       </c>
@@ -7862,7 +7857,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>337</v>
       </c>
@@ -7885,7 +7880,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>337</v>
       </c>
@@ -7908,7 +7903,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>337</v>
       </c>
@@ -7931,7 +7926,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>337</v>
       </c>
@@ -7954,7 +7949,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>337</v>
       </c>
@@ -7977,7 +7972,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>337</v>
       </c>
@@ -8000,7 +7995,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>337</v>
       </c>
@@ -8023,7 +8018,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>337</v>
       </c>
@@ -8046,7 +8041,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>337</v>
       </c>
@@ -8069,7 +8064,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>337</v>
       </c>
@@ -8092,7 +8087,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>337</v>
       </c>
@@ -8115,10 +8110,40 @@
         <v>15</v>
       </c>
     </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G268" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G269" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G270" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G271" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G272" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="273" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G273" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G267"/>
+  <autoFilter ref="A1:G267" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G267">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G273" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$Q$2:$Q$11</formula1>
     </dataValidation>
   </dataValidations>

--- a/public/data/ministries_pvp.xlsx
+++ b/public/data/ministries_pvp.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\vacantPositionsPowerBI\OPSC PVP Dashboard\psc-pvp-dashboard\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{461D5CA6-4FBA-4753-8DD2-736FE7C3B445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{37ADED4C-AF66-4EC7-8D4D-C245FAE75031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="36465" yWindow="870" windowWidth="21600" windowHeight="11235"/>
   </bookViews>
   <sheets>
-    <sheet name="ministries_pvp" sheetId="1" r:id="rId1"/>
+    <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ministries_pvp!$A$1:$G$267</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$G$267</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
